--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -499,7 +499,7 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2871</v>
+        <v>0.2916</v>
       </c>
     </row>
     <row r="3">
@@ -520,7 +520,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -538,7 +538,7 @@
         <v>1.01</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1669</v>
+        <v>0.1701</v>
       </c>
     </row>
     <row r="4">
@@ -549,24 +549,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2359 HK</t>
+          <t>522 HK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>ASMPT</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diagnostics &amp; Research</t>
+          <t>半导体设备与材料</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="F4" t="n">
-        <v>0.73</v>
+        <v>0.61</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         <v>1.01</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1392</v>
+        <v>0.1813</v>
       </c>
     </row>
     <row r="5">
@@ -588,24 +588,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>522 HK</t>
+          <t>9992 HK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ASMPT</t>
+          <t>泡泡玛特</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>潮玩IP</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="F5" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         <v>1.01</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1812</v>
+        <v>0.1313</v>
       </c>
     </row>
     <row r="6">
@@ -627,24 +627,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2338 HK</t>
+          <t>3993 HK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>潍柴动力</t>
+          <t>洛阳钼业</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Auto Manufacturers</t>
+          <t>工业金属与矿业</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1536</v>
+        <v>0.1488</v>
       </c>
     </row>
     <row r="7">
@@ -666,24 +666,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2018 HK</t>
+          <t>1208 HK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>瑞声科技</t>
+          <t>五矿资源</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>铜</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="F7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1835</v>
+        <v>0.1836</v>
       </c>
     </row>
     <row r="8">
@@ -705,24 +705,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STX US</t>
+          <t>WDC US</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>希捷科技</t>
+          <t>西部数据</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2921</v>
+        <v>0.2823</v>
       </c>
     </row>
     <row r="9">
@@ -744,24 +744,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WDC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>西部数据</t>
+          <t>Credo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>AI互联</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2837</v>
+        <v>0.2582</v>
       </c>
     </row>
     <row r="10">
@@ -783,17 +783,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Credo</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AI互联</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -811,7 +811,7 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.27</v>
+        <v>0.2796</v>
       </c>
     </row>
     <row r="11">
@@ -822,25 +822,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>STX US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>希捷科技</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.4</v>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>欧式敲入</t>
@@ -850,7 +850,7 @@
         <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.281</v>
+        <v>0.2937</v>
       </c>
     </row>
     <row r="12">
@@ -861,24 +861,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>DELL US</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Marvell</t>
+          <t>戴尔科技</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>客制硅/互联</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
         <v>1.01</v>
       </c>
       <c r="I12" t="n">
-        <v>0.265</v>
+        <v>0.283</v>
       </c>
     </row>
     <row r="13">
@@ -900,24 +900,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DELL US</t>
+          <t>KLAC US</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>戴尔科技</t>
+          <t>科磊</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>半导体设备与材料</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="F13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>1.01</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2732</v>
+        <v>0.2975</v>
       </c>
     </row>
     <row r="14">
@@ -939,24 +939,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LRCX US</t>
+          <t>AMAT US</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>泛林集团</t>
+          <t>应用材料</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>半导体设备与材料</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="F14" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2958</v>
+        <v>0.2949</v>
       </c>
     </row>
     <row r="15">
@@ -978,24 +978,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMAT US</t>
+          <t>LRCX US</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>应用材料</t>
+          <t>泛林集团</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>半导体设备与材料</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="F15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2991</v>
+        <v>0.2877</v>
       </c>
     </row>
     <row r="16">
@@ -1017,24 +1017,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KLAC US</t>
+          <t>RDDT US</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>科磊</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>互联网内容与信息</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="F16" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>1.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3281</v>
+        <v>0.288</v>
       </c>
     </row>
     <row r="17">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CIEN US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>慧与科技</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.65</v>
+        <v>0.76</v>
       </c>
       <c r="F17" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2814</v>
+        <v>0.2712</v>
       </c>
     </row>
     <row r="18">
@@ -1095,24 +1095,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>CIEN US</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>慧与科技</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.76</v>
+        <v>0.65</v>
       </c>
       <c r="F18" t="n">
-        <v>0.66</v>
+        <v>0.55</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>1.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2717</v>
+        <v>0.276</v>
       </c>
     </row>
     <row r="19">
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F19" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2764</v>
+        <v>0.281</v>
       </c>
     </row>
     <row r="20">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>专用工业机械</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1201,7 +1201,7 @@
         <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2069</v>
+        <v>0.2061</v>
       </c>
     </row>
     <row r="21">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>航空航天与国防</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1240,7 +1240,7 @@
         <v>1.01</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1272</v>
+        <v>0.1258</v>
       </c>
     </row>
   </sheetData>

--- a/高波精选组.xlsx
+++ b/高波精选组.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -46,11 +52,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,7 +422,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -471,24 +479,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1347 HK</t>
+          <t>992 HK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>华虹宏力</t>
+          <t>联想集团</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.68</v>
+        <v>0.75</v>
       </c>
       <c r="F2" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -498,8 +506,8 @@
       <c r="H2" t="n">
         <v>1.01</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.2916</v>
+      <c r="I2" s="2" t="n">
+        <v>0.1913</v>
       </c>
     </row>
     <row r="3">
@@ -510,24 +518,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>992 HK</t>
+          <t>9992 HK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>联想集团</t>
+          <t>泡泡玛特</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>计算机硬件</t>
+          <t>潮玩IP</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="F3" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -537,8 +545,8 @@
       <c r="H3" t="n">
         <v>1.01</v>
       </c>
-      <c r="I3" t="n">
-        <v>0.1701</v>
+      <c r="I3" s="2" t="n">
+        <v>0.1538</v>
       </c>
     </row>
     <row r="4">
@@ -549,24 +557,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>522 HK</t>
+          <t>1347 HK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASMPT</t>
+          <t>华虹宏力</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>半导体设备与材料</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.71</v>
+        <v>0.66</v>
       </c>
       <c r="F4" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,8 +584,8 @@
       <c r="H4" t="n">
         <v>1.01</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.1813</v>
+      <c r="I4" s="2" t="n">
+        <v>0.2595</v>
       </c>
     </row>
     <row r="5">
@@ -588,24 +596,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9992 HK</t>
+          <t>522 HK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>泡泡玛特</t>
+          <t>ASMPT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>潮玩IP</t>
+          <t>半导体设备与材料</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -615,8 +623,8 @@
       <c r="H5" t="n">
         <v>1.01</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.1313</v>
+      <c r="I5" s="2" t="n">
+        <v>0.2428</v>
       </c>
     </row>
     <row r="6">
@@ -627,24 +635,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3993 HK</t>
+          <t>6869 HK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>洛阳钼业</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>工业金属与矿业</t>
+          <t>AI光通信</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="F6" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,8 +662,8 @@
       <c r="H6" t="n">
         <v>1.01</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.1488</v>
+      <c r="I6" s="2" t="n">
+        <v>0.3629</v>
       </c>
     </row>
     <row r="7">
@@ -666,24 +674,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1208 HK</t>
+          <t>9995 HK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>五矿资源</t>
+          <t>荣昌生物</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>铜</t>
+          <t>生物科技</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -693,8 +701,8 @@
       <c r="H7" t="n">
         <v>1.01</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.1836</v>
+      <c r="I7" s="2" t="n">
+        <v>0.2264</v>
       </c>
     </row>
     <row r="8">
@@ -705,24 +713,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WDC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>西部数据</t>
+          <t>Credo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>计算机硬件</t>
+          <t>AI互联</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.59</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.49</v>
+        <v>0.4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -732,8 +740,8 @@
       <c r="H8" t="n">
         <v>1.01</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.2823</v>
+      <c r="I8" s="2" t="n">
+        <v>0.2935</v>
       </c>
     </row>
     <row r="9">
@@ -744,24 +752,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>STX US</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Credo</t>
+          <t>希捷科技</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AI互联</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -771,8 +779,8 @@
       <c r="H9" t="n">
         <v>1.01</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.2582</v>
+      <c r="I9" s="2" t="n">
+        <v>0.2891</v>
       </c>
     </row>
     <row r="10">
@@ -783,24 +791,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>MU US</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>美光</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>半导体</t>
+          <t>内存/HBM</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -810,8 +818,8 @@
       <c r="H10" t="n">
         <v>1.01</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.2796</v>
+      <c r="I10" s="2" t="n">
+        <v>0.3012</v>
       </c>
     </row>
     <row r="11">
@@ -822,12 +830,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STX US</t>
+          <t>WDC US</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>希捷科技</t>
+          <t>西部数据</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -836,10 +844,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -849,8 +857,8 @@
       <c r="H11" t="n">
         <v>1.01</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.2937</v>
+      <c r="I11" s="2" t="n">
+        <v>0.2862</v>
       </c>
     </row>
     <row r="12">
@@ -861,24 +869,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DELL US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>戴尔科技</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>计算机硬件</t>
+          <t>半导体</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="F12" t="n">
-        <v>0.59</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -888,8 +896,8 @@
       <c r="H12" t="n">
         <v>1.01</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.283</v>
+      <c r="I12" s="2" t="n">
+        <v>0.2713</v>
       </c>
     </row>
     <row r="13">
@@ -900,24 +908,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KLAC US</t>
+          <t>DELL US</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>科磊</t>
+          <t>戴尔科技</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>半导体设备与材料</t>
+          <t>计算机硬件</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -927,8 +935,8 @@
       <c r="H13" t="n">
         <v>1.01</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.2975</v>
+      <c r="I13" s="2" t="n">
+        <v>0.2954</v>
       </c>
     </row>
     <row r="14">
@@ -939,24 +947,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMAT US</t>
+          <t>AMD US</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>应用材料</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>半导体设备与材料</t>
+          <t>AI芯片</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="F14" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -966,8 +974,8 @@
       <c r="H14" t="n">
         <v>1.01</v>
       </c>
-      <c r="I14" t="n">
-        <v>0.2949</v>
+      <c r="I14" s="2" t="n">
+        <v>0.2847</v>
       </c>
     </row>
     <row r="15">
@@ -978,12 +986,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LRCX US</t>
+          <t>AMAT US</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>泛林集团</t>
+          <t>应用材料</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1005,8 +1013,8 @@
       <c r="H15" t="n">
         <v>1.01</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.2877</v>
+      <c r="I15" s="2" t="n">
+        <v>0.303</v>
       </c>
     </row>
     <row r="16">
@@ -1017,24 +1025,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RDDT US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>慧与科技</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>互联网内容与信息</t>
+          <t>通信设备</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="F16" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1044,8 +1052,8 @@
       <c r="H16" t="n">
         <v>1.01</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.288</v>
+      <c r="I16" s="2" t="n">
+        <v>0.2832</v>
       </c>
     </row>
     <row r="17">
@@ -1056,24 +1064,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>DDOG US</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>慧与科技</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>应用软件</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="F17" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1083,8 +1091,8 @@
       <c r="H17" t="n">
         <v>1.01</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.2712</v>
+      <c r="I17" s="2" t="n">
+        <v>0.2862</v>
       </c>
     </row>
     <row r="18">
@@ -1095,25 +1103,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CIEN US</t>
+          <t>RDDT US</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>通信设备</t>
+          <t>互联网内容与信息</t>
         </is>
       </c>
       <c r="E18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.65</v>
       </c>
-      <c r="F18" t="n">
-        <v>0.55</v>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>欧式敲入</t>
@@ -1122,8 +1130,8 @@
       <c r="H18" t="n">
         <v>1.01</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.276</v>
+      <c r="I18" s="2" t="n">
+        <v>0.3099</v>
       </c>
     </row>
     <row r="19">
@@ -1134,24 +1142,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>数据中心冷却</t>
+          <t>专用工业机械</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1161,8 +1169,8 @@
       <c r="H19" t="n">
         <v>1.01</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.281</v>
+      <c r="I19" s="2" t="n">
+        <v>0.2132</v>
       </c>
     </row>
     <row r="20">
@@ -1173,24 +1181,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>HOOD US</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>专用工业机械</t>
+          <t>券商/加密</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1200,8 +1208,8 @@
       <c r="H20" t="n">
         <v>1.01</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.2061</v>
+      <c r="I20" s="2" t="n">
+        <v>0.2854</v>
       </c>
     </row>
     <row r="21">
@@ -1212,24 +1220,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HWM US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>航空航天与国防</t>
+          <t>数据中心冷却</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="F21" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1239,8 +1247,8 @@
       <c r="H21" t="n">
         <v>1.01</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.1258</v>
+      <c r="I21" s="2" t="n">
+        <v>0.2935</v>
       </c>
     </row>
   </sheetData>
